--- a/reports/2026-08_月次実績報告/excel/第51期下期松江営業所担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期松江営業所担当者別実績.xlsx
@@ -5814,7 +5814,10 @@
         <v>0</v>
       </c>
       <c r="J67" s="39" t="n"/>
-      <c r="K67" s="79" t="n"/>
+      <c r="K67" s="39">
+        <f>SUM(E67:J67)</f>
+        <v/>
+      </c>
       <c r="L67" s="58" t="n">
         <v>9</v>
       </c>
@@ -5827,7 +5830,10 @@
         <v>0</v>
       </c>
       <c r="Q67" s="39" t="n"/>
-      <c r="R67" s="75" t="n"/>
+      <c r="R67" s="39">
+        <f>SUM(L67:Q67)</f>
+        <v/>
+      </c>
       <c r="S67" s="115">
         <f>IF(E67=0,"***",L67/E67)</f>
         <v/>
@@ -11989,7 +11995,10 @@
         <v/>
       </c>
       <c r="J67" s="39" t="n"/>
-      <c r="K67" s="79" t="n"/>
+      <c r="K67" s="39">
+        <f>SUM(E67:J67)</f>
+        <v/>
+      </c>
       <c r="L67" s="81">
         <f>全体!L67-機械!L67</f>
         <v/>
@@ -12011,7 +12020,10 @@
         <v/>
       </c>
       <c r="Q67" s="39" t="n"/>
-      <c r="R67" s="75" t="n"/>
+      <c r="R67" s="39">
+        <f>SUM(L67:Q67)</f>
+        <v/>
+      </c>
       <c r="S67" s="115">
         <f>IF(E67=0,"***",L67/E67)</f>
         <v/>
@@ -13201,19 +13213,19 @@
         <v/>
       </c>
       <c r="U85" s="116">
-        <f>U75-U45</f>
+        <f>U65-U15</f>
         <v/>
       </c>
       <c r="V85" s="116">
-        <f>V75-V45</f>
+        <f>V65-V15</f>
         <v/>
       </c>
       <c r="W85" s="116">
-        <f>W75-W45</f>
+        <f>W65-W15</f>
         <v/>
       </c>
       <c r="X85" s="116">
-        <f>X75-X45</f>
+        <f>X65-X15</f>
         <v/>
       </c>
       <c r="Y85" s="117">
@@ -13291,19 +13303,19 @@
         <v/>
       </c>
       <c r="U86" s="116">
-        <f>U76-U46</f>
+        <f>U66-U16</f>
         <v/>
       </c>
       <c r="V86" s="116">
-        <f>V76-V46</f>
+        <f>V66-V16</f>
         <v/>
       </c>
       <c r="W86" s="116">
-        <f>W76-W46</f>
+        <f>W66-W16</f>
         <v/>
       </c>
       <c r="X86" s="116">
-        <f>X76-X46</f>
+        <f>X66-X16</f>
         <v/>
       </c>
       <c r="Y86" s="117">
@@ -13381,19 +13393,19 @@
         <v/>
       </c>
       <c r="U87" s="116">
-        <f>U77-U47</f>
+        <f>U67-U17</f>
         <v/>
       </c>
       <c r="V87" s="116">
-        <f>V77-V47</f>
+        <f>V67-V17</f>
         <v/>
       </c>
       <c r="W87" s="116">
-        <f>W77-W47</f>
+        <f>W67-W17</f>
         <v/>
       </c>
       <c r="X87" s="116">
-        <f>X77-X47</f>
+        <f>X67-X17</f>
         <v/>
       </c>
       <c r="Y87" s="117">
@@ -13471,19 +13483,19 @@
         <v/>
       </c>
       <c r="U88" s="116">
-        <f>U78-U48</f>
+        <f>U68-U18</f>
         <v/>
       </c>
       <c r="V88" s="116">
-        <f>V78-V48</f>
+        <f>V68-V18</f>
         <v/>
       </c>
       <c r="W88" s="116">
-        <f>W78-W48</f>
+        <f>W68-W18</f>
         <v/>
       </c>
       <c r="X88" s="116">
-        <f>X78-X48</f>
+        <f>X68-X18</f>
         <v/>
       </c>
       <c r="Y88" s="117">
@@ -13561,19 +13573,19 @@
         <v/>
       </c>
       <c r="U89" s="116">
-        <f>U79-U49</f>
+        <f>U69-U19</f>
         <v/>
       </c>
       <c r="V89" s="116">
-        <f>V79-V49</f>
+        <f>V69-V19</f>
         <v/>
       </c>
       <c r="W89" s="116">
-        <f>W79-W49</f>
+        <f>W69-W19</f>
         <v/>
       </c>
       <c r="X89" s="116">
-        <f>X79-X49</f>
+        <f>X69-X19</f>
         <v/>
       </c>
       <c r="Y89" s="117">
@@ -18601,7 +18613,7 @@
         <v/>
       </c>
       <c r="X75" s="116">
-        <f>X55-X5</f>
+        <f>X65-X35</f>
         <v/>
       </c>
       <c r="Y75" s="117">
@@ -18691,7 +18703,7 @@
         <v/>
       </c>
       <c r="X76" s="116">
-        <f>X56-X6</f>
+        <f>X66-X36</f>
         <v/>
       </c>
       <c r="Y76" s="117">
@@ -18781,7 +18793,7 @@
         <v/>
       </c>
       <c r="X77" s="116">
-        <f>X57-X7</f>
+        <f>X67-X37</f>
         <v/>
       </c>
       <c r="Y77" s="117">
@@ -18871,7 +18883,7 @@
         <v/>
       </c>
       <c r="X78" s="116">
-        <f>X58-X8</f>
+        <f>X68-X38</f>
         <v/>
       </c>
       <c r="Y78" s="117">
@@ -18961,7 +18973,7 @@
         <v/>
       </c>
       <c r="X79" s="116">
-        <f>X59-X9</f>
+        <f>X69-X39</f>
         <v/>
       </c>
       <c r="Y79" s="117">
@@ -19272,19 +19284,19 @@
         <v/>
       </c>
       <c r="U85" s="116">
-        <f>U75-U45</f>
+        <f>U65-U15</f>
         <v/>
       </c>
       <c r="V85" s="116">
-        <f>V75-V45</f>
+        <f>V65-V15</f>
         <v/>
       </c>
       <c r="W85" s="116">
-        <f>W75-W45</f>
+        <f>W65-W15</f>
         <v/>
       </c>
       <c r="X85" s="116">
-        <f>X75-X45</f>
+        <f>X65-X15</f>
         <v/>
       </c>
       <c r="Y85" s="117">
@@ -19362,19 +19374,19 @@
         <v/>
       </c>
       <c r="U86" s="116">
-        <f>U76-U46</f>
+        <f>U66-U16</f>
         <v/>
       </c>
       <c r="V86" s="116">
-        <f>V76-V46</f>
+        <f>V66-V16</f>
         <v/>
       </c>
       <c r="W86" s="116">
-        <f>W76-W46</f>
+        <f>W66-W16</f>
         <v/>
       </c>
       <c r="X86" s="116">
-        <f>X76-X46</f>
+        <f>X66-X16</f>
         <v/>
       </c>
       <c r="Y86" s="117">
@@ -19452,19 +19464,19 @@
         <v/>
       </c>
       <c r="U87" s="116">
-        <f>U77-U47</f>
+        <f>U67-U17</f>
         <v/>
       </c>
       <c r="V87" s="116">
-        <f>V77-V47</f>
+        <f>V67-V17</f>
         <v/>
       </c>
       <c r="W87" s="116">
-        <f>W77-W47</f>
+        <f>W67-W17</f>
         <v/>
       </c>
       <c r="X87" s="116">
-        <f>X77-X47</f>
+        <f>X67-X17</f>
         <v/>
       </c>
       <c r="Y87" s="117">
@@ -19542,19 +19554,19 @@
         <v/>
       </c>
       <c r="U88" s="116">
-        <f>U78-U48</f>
+        <f>U68-U18</f>
         <v/>
       </c>
       <c r="V88" s="116">
-        <f>V78-V48</f>
+        <f>V68-V18</f>
         <v/>
       </c>
       <c r="W88" s="116">
-        <f>W78-W48</f>
+        <f>W68-W18</f>
         <v/>
       </c>
       <c r="X88" s="116">
-        <f>X78-X48</f>
+        <f>X68-X18</f>
         <v/>
       </c>
       <c r="Y88" s="117">
@@ -19632,19 +19644,19 @@
         <v/>
       </c>
       <c r="U89" s="116">
-        <f>U79-U49</f>
+        <f>U69-U19</f>
         <v/>
       </c>
       <c r="V89" s="116">
-        <f>V79-V49</f>
+        <f>V69-V19</f>
         <v/>
       </c>
       <c r="W89" s="116">
-        <f>W79-W49</f>
+        <f>W69-W19</f>
         <v/>
       </c>
       <c r="X89" s="116">
-        <f>X79-X49</f>
+        <f>X69-X19</f>
         <v/>
       </c>
       <c r="Y89" s="117">

--- a/reports/2026-08_月次実績報告/excel/第51期下期松江営業所担当者別実績.xlsx
+++ b/reports/2026-08_月次実績報告/excel/第51期下期松江営業所担当者別実績.xlsx
@@ -18042,7 +18042,7 @@
         <v>3549.9651</v>
       </c>
       <c r="P66" s="2" t="n">
-        <v>2625.623</v>
+        <v>2620.623</v>
       </c>
       <c r="Q66" s="2" t="n"/>
       <c r="R66" s="75">
